--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_5_14.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_5_14.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319018.5656753904</v>
+        <v>313213.0340391589</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547407</v>
+        <v>3007417.133686139</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745724</v>
+        <v>20367601.51138412</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4814095.689442963</v>
+        <v>4798096.092123126</v>
       </c>
     </row>
     <row r="11">
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1256,13 +1256,13 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1323,22 +1323,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.54368386855044</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1417,16 +1417,16 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1451,16 +1451,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>22.15420867374214</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1530,19 +1530,19 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1606,16 +1606,16 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>22.90079999999999</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1642,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1733,16 +1733,16 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y15" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
     </row>
     <row r="16">
@@ -1755,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1767,16 +1767,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2741920426674241</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1831,31 +1831,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>12.71311064538747</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1922,16 +1922,16 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>23.91580867374214</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0.7465913262578567</v>
@@ -1964,13 +1964,13 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>23.55470292302859</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -2040,19 +2040,19 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="T19" t="n">
-        <v>22.02246762618612</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2068,19 +2068,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2113,22 +2113,22 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>62.4162677022923</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>11.16618163507844</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>131.8008223430613</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>88.55090549590538</v>
       </c>
       <c r="Y21" t="n">
         <v>205.6826957773044</v>
@@ -2280,16 +2280,16 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2308,22 +2308,22 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2353,13 +2353,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2368,10 +2368,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>84.39291325806006</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2399,10 +2399,10 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>45.84493760018498</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2435,25 +2435,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>102.2504373005607</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2545,13 +2545,13 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2587,31 +2587,31 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>26.93035592563413</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>184.6308886574542</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>90.38893773807641</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2824,28 +2824,28 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>212.2728</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2876,13 +2876,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2906,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>29.01125423986463</v>
+        <v>23.17871577922039</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2979,19 +2979,19 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>189.3719999999999</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3061,19 +3061,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>11.19305615617957</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3104,16 +3104,16 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3152,7 +3152,7 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>112.0407133227324</v>
+        <v>99.24815076615349</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -3195,10 +3195,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>39.82778746869524</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3310,16 +3310,16 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3341,22 +3341,22 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>134.4914753081025</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364965</v>
+        <v>68.23671972608848</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3386,19 +3386,19 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>215</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>130.4655268502615</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3496,25 +3496,25 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="G38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>179.7283339446664</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3538,16 +3538,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>17.56289348969301</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3569,22 +3569,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>57.46423735114152</v>
+        <v>91.01404827120736</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3617,16 +3617,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3742,16 +3742,16 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>29.77192311799241</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3775,10 +3775,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>82.69225998619919</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3824,13 +3824,13 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3860,22 +3860,22 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>33.96385134055175</v>
       </c>
     </row>
     <row r="43">
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82000000000018</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56000000000017</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.30000000000017</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348994</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>103.6392766348994</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>103.72303834074</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>77.46041207811371</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F14" t="n">
-        <v>77.73737373737373</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="G14" t="n">
-        <v>51.47474747474747</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="H14" t="n">
-        <v>25.2121212121212</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>26.78000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L14" t="n">
-        <v>52.52000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M14" t="n">
-        <v>78.26000000000001</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N14" t="n">
-        <v>104</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O14" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25.2121212121212</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C15" t="n">
-        <v>25.2121212121212</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D15" t="n">
-        <v>25.2121212121212</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E15" t="n">
-        <v>25.2121212121212</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M15" t="n">
-        <v>27.82</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N15" t="n">
-        <v>27.82</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O15" t="n">
-        <v>52.52000000000001</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V15" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W15" t="n">
-        <v>51.47474747474747</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X15" t="n">
-        <v>51.47474747474747</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="Y15" t="n">
-        <v>25.2121212121212</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="D16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="E16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="F16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="G16" t="n">
-        <v>77.73737373737373</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y16" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="C17" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="D17" t="n">
-        <v>55.43434343434343</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="E17" t="n">
-        <v>55.43434343434343</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="F17" t="n">
-        <v>42.59281752991163</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="G17" t="n">
-        <v>14.30998924708335</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="H17" t="n">
-        <v>14.30998924708335</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="I17" t="n">
-        <v>14.30998924708335</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L17" t="n">
-        <v>29.96</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="M17" t="n">
-        <v>29.96</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="N17" t="n">
-        <v>57.68</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O17" t="n">
-        <v>85.40000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="U17" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="V17" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="W17" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="X17" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="Y17" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>112</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="C18" t="n">
-        <v>112</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="D18" t="n">
-        <v>112</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="F18" t="n">
-        <v>87.84261750127057</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="G18" t="n">
-        <v>59.55978921844228</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="H18" t="n">
-        <v>31.276960935614</v>
+        <v>2.961334673611005</v>
       </c>
       <c r="I18" t="n">
-        <v>2.994132652785714</v>
+        <v>2.961334673611005</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L18" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>2.24</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N18" t="n">
-        <v>29.96</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O18" t="n">
-        <v>57.68</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P18" t="n">
-        <v>85.40000000000001</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T18" t="n">
-        <v>112</v>
+        <v>86.56747182608416</v>
       </c>
       <c r="U18" t="n">
-        <v>112</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="V18" t="n">
-        <v>112</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="W18" t="n">
-        <v>112</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="X18" t="n">
-        <v>112</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="Y18" t="n">
-        <v>112</v>
+        <v>30.83004705776872</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>109.3334016426122</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="T19" t="n">
-        <v>87.08848484848485</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="U19" t="n">
-        <v>58.80565656565657</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="V19" t="n">
-        <v>30.52282828282829</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C20" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>953.9083846317729</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S20" t="n">
-        <v>742.7770012113231</v>
+        <v>749.627473042513</v>
       </c>
       <c r="T20" t="n">
-        <v>517.427658217251</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U20" t="n">
-        <v>273.9933147829075</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V20" t="n">
-        <v>262.7143434343434</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W20" t="n">
-        <v>262.7143434343434</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X20" t="n">
-        <v>262.7143434343434</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y20" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>152.41214378087</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>487.8331058683492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>588.3960608094349</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>360.1724425458239</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W21" t="n">
-        <v>360.1724425458239</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="X21" t="n">
-        <v>360.1724425458239</v>
+        <v>396.0109115480204</v>
       </c>
       <c r="Y21" t="n">
-        <v>152.41214378087</v>
+        <v>188.2506127830665</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>262.7143434343434</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C23" t="n">
-        <v>19.28</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D23" t="n">
-        <v>19.28</v>
+        <v>749.627473042513</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S23" t="n">
-        <v>591.3940537960203</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T23" t="n">
-        <v>591.3940537960203</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U23" t="n">
-        <v>591.3940537960203</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V23" t="n">
-        <v>591.3940537960203</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W23" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X23" t="n">
-        <v>262.7143434343434</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y23" t="n">
-        <v>262.7143434343434</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>417.9145189829202</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="C24" t="n">
-        <v>417.9145189829202</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="D24" t="n">
-        <v>417.9145189829202</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="E24" t="n">
-        <v>417.9145189829202</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="F24" t="n">
-        <v>271.3799610098052</v>
+        <v>65.58916088817736</v>
       </c>
       <c r="G24" t="n">
-        <v>132.6491355924207</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M24" t="n">
-        <v>383.2275600578374</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N24" t="n">
-        <v>621.8175600578375</v>
+        <v>621.8469951458151</v>
       </c>
       <c r="O24" t="n">
-        <v>860.4075600578375</v>
+        <v>860.4511411346975</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S24" t="n">
-        <v>689.4131260035546</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T24" t="n">
-        <v>586.1298560029882</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U24" t="n">
-        <v>586.1298560029882</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V24" t="n">
-        <v>586.1298560029882</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="W24" t="n">
-        <v>586.1298560029882</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="X24" t="n">
-        <v>586.1298560029882</v>
+        <v>419.8840176262463</v>
       </c>
       <c r="Y24" t="n">
-        <v>586.1298560029882</v>
+        <v>212.1237188612924</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C26" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V26" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W26" t="n">
-        <v>262.7143434343434</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X26" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y26" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>380.1728640094453</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="C27" t="n">
-        <v>205.7198347283183</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D27" t="n">
-        <v>205.7198347283183</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E27" t="n">
-        <v>46.48237972286276</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>248.2447175439888</v>
       </c>
       <c r="M27" t="n">
-        <v>374.6006659261865</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N27" t="n">
-        <v>542.7665223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W27" t="n">
-        <v>964</v>
+        <v>777.5613083818946</v>
       </c>
       <c r="X27" t="n">
-        <v>756.1484997944672</v>
+        <v>569.7098081763618</v>
       </c>
       <c r="Y27" t="n">
-        <v>548.3882010295133</v>
+        <v>361.9495094114078</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.28</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T29" t="n">
-        <v>749.5830303030303</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U29" t="n">
-        <v>506.1486868686869</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="V29" t="n">
-        <v>262.7143434343434</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="W29" t="n">
-        <v>19.28</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="X29" t="n">
-        <v>19.28</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.28</v>
+        <v>122.6530896684844</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="C30" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="D30" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="E30" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="F30" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="G30" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H30" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M30" t="n">
-        <v>374.6006659261865</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N30" t="n">
-        <v>473.3719638733197</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S30" t="n">
-        <v>934.6957027880155</v>
+        <v>839.4747818420872</v>
       </c>
       <c r="T30" t="n">
-        <v>934.6957027880155</v>
+        <v>839.4747818420872</v>
       </c>
       <c r="U30" t="n">
-        <v>706.4720845244046</v>
+        <v>611.2511635784762</v>
       </c>
       <c r="V30" t="n">
-        <v>471.319976292662</v>
+        <v>376.0990553467335</v>
       </c>
       <c r="W30" t="n">
-        <v>227.8856328583186</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="X30" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="Y30" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>425.6565656565656</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C32" t="n">
-        <v>425.6565656565656</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D32" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E32" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F32" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>513.1408574955809</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>718.9953797028202</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>942.6594228129348</v>
       </c>
       <c r="S32" t="n">
-        <v>860</v>
+        <v>731.528039392485</v>
       </c>
       <c r="T32" t="n">
-        <v>860</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="U32" t="n">
-        <v>860</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="V32" t="n">
-        <v>860</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W32" t="n">
-        <v>860</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X32" t="n">
-        <v>642.8282828282828</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y32" t="n">
-        <v>425.6565656565656</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>270.0540936625908</v>
+        <v>179.2727307684539</v>
       </c>
       <c r="C33" t="n">
-        <v>270.0540936625908</v>
+        <v>179.2727307684539</v>
       </c>
       <c r="D33" t="n">
-        <v>270.0540936625908</v>
+        <v>179.2727307684539</v>
       </c>
       <c r="E33" t="n">
-        <v>270.0540936625908</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F33" t="n">
-        <v>270.0540936625908</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G33" t="n">
-        <v>131.3232682452064</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H33" t="n">
-        <v>17.95413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I33" t="n">
-        <v>17.95413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>355.4075600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M33" t="n">
-        <v>464.5065223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N33" t="n">
-        <v>464.5065223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O33" t="n">
-        <v>677.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>758.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S33" t="n">
-        <v>585.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T33" t="n">
-        <v>383.2265313623206</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U33" t="n">
-        <v>270.0540936625908</v>
+        <v>387.0330295334078</v>
       </c>
       <c r="V33" t="n">
-        <v>270.0540936625908</v>
+        <v>387.0330295334078</v>
       </c>
       <c r="W33" t="n">
-        <v>270.0540936625908</v>
+        <v>387.0330295334078</v>
       </c>
       <c r="X33" t="n">
-        <v>270.0540936625908</v>
+        <v>387.0330295334078</v>
       </c>
       <c r="Y33" t="n">
-        <v>270.0540936625908</v>
+        <v>179.2727307684539</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>819.7699116477826</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>752.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>791.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>835.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>860</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>860</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>860</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y34" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.2</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="C35" t="n">
-        <v>17.2</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="D35" t="n">
-        <v>17.2</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>22.36462077340309</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U35" t="n">
-        <v>668.7151515151515</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V35" t="n">
-        <v>451.5434343434343</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W35" t="n">
-        <v>234.3717171717172</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X35" t="n">
-        <v>17.2</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y35" t="n">
-        <v>17.2</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>425.6565656565656</v>
+        <v>325.7954424002585</v>
       </c>
       <c r="C36" t="n">
-        <v>425.6565656565656</v>
+        <v>325.7954424002585</v>
       </c>
       <c r="D36" t="n">
-        <v>425.6565656565656</v>
+        <v>325.7954424002585</v>
       </c>
       <c r="E36" t="n">
-        <v>266.4191106511101</v>
+        <v>325.7954424002585</v>
       </c>
       <c r="F36" t="n">
-        <v>130.5691355924207</v>
+        <v>179.2608844271435</v>
       </c>
       <c r="G36" t="n">
-        <v>130.5691355924207</v>
+        <v>179.2608844271435</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>230.05</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M36" t="n">
-        <v>364.9054414866706</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N36" t="n">
-        <v>577.7554414866706</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O36" t="n">
-        <v>790.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P36" t="n">
-        <v>790.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U36" t="n">
-        <v>642.8282828282828</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V36" t="n">
-        <v>425.6565656565656</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="W36" t="n">
-        <v>425.6565656565656</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="X36" t="n">
-        <v>425.6565656565656</v>
+        <v>325.7954424002585</v>
       </c>
       <c r="Y36" t="n">
-        <v>425.6565656565656</v>
+        <v>325.7954424002585</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C37" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D37" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="U37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="V37" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W37" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X37" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y37" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>246.4417064188005</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="C38" t="n">
-        <v>246.4417064188005</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="D38" t="n">
-        <v>246.4417064188005</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="E38" t="n">
-        <v>246.4417064188005</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="F38" t="n">
-        <v>246.4417064188005</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="G38" t="n">
-        <v>29.26998924708335</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="H38" t="n">
-        <v>29.26998924708335</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="I38" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M38" t="n">
-        <v>504.9505276501126</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N38" t="n">
-        <v>710.8050498573519</v>
+        <v>719.4169572236606</v>
       </c>
       <c r="O38" t="n">
-        <v>860</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R38" t="n">
-        <v>698.5254372164702</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S38" t="n">
-        <v>680.7851407622348</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T38" t="n">
-        <v>463.6134235905177</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="U38" t="n">
-        <v>246.4417064188005</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="V38" t="n">
-        <v>246.4417064188005</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="W38" t="n">
-        <v>246.4417064188005</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="X38" t="n">
-        <v>246.4417064188005</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="Y38" t="n">
-        <v>246.4417064188005</v>
+        <v>851.4843753638859</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>388.4285388915837</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="C39" t="n">
-        <v>213.9755096104567</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="D39" t="n">
-        <v>155.9308254173845</v>
+        <v>176.4689748200978</v>
       </c>
       <c r="E39" t="n">
-        <v>155.9308254173845</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F39" t="n">
-        <v>155.9308254173845</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L39" t="n">
-        <v>230.05</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="M39" t="n">
-        <v>442.9</v>
+        <v>443.7116352270382</v>
       </c>
       <c r="N39" t="n">
-        <v>442.9</v>
+        <v>648.335933025915</v>
       </c>
       <c r="O39" t="n">
-        <v>607.9619638733197</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>758.8304705528857</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S39" t="n">
-        <v>758.8304705528857</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="T39" t="n">
-        <v>556.6438759116518</v>
+        <v>485.9720515415478</v>
       </c>
       <c r="U39" t="n">
-        <v>556.6438759116518</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="V39" t="n">
-        <v>556.6438759116518</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="W39" t="n">
-        <v>556.6438759116518</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="X39" t="n">
-        <v>556.6438759116518</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="Y39" t="n">
-        <v>556.6438759116518</v>
+        <v>268.4023569122264</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>752.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>791.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>835.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U40" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V40" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>274.3341540127323</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="C41" t="n">
-        <v>274.3341540127323</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="D41" t="n">
-        <v>274.3341540127323</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="E41" t="n">
-        <v>274.3341540127323</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="F41" t="n">
-        <v>274.3341540127323</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="G41" t="n">
-        <v>59.1826388612171</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>59.1826388612171</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>29.10998924708335</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1308574955809</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>700.6170525846973</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>489.4856691642474</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>489.4856691642474</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>489.4856691642474</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V41" t="n">
-        <v>274.3341540127323</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="W41" t="n">
-        <v>274.3341540127323</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="X41" t="n">
-        <v>274.3341540127323</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Y41" t="n">
-        <v>274.3341540127323</v>
+        <v>853.6970544693717</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="C42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="D42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="E42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="F42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="G42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>219.8269915258632</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>431.1170125070327</v>
       </c>
       <c r="N42" t="n">
-        <v>775.0075600578374</v>
+        <v>642.4070334882022</v>
       </c>
       <c r="O42" t="n">
-        <v>782.6054414866707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>651.5104598281378</v>
       </c>
       <c r="U42" t="n">
-        <v>636.8484848484849</v>
+        <v>651.5104598281378</v>
       </c>
       <c r="V42" t="n">
-        <v>636.8484848484849</v>
+        <v>435.9303955681954</v>
       </c>
       <c r="W42" t="n">
-        <v>421.6969696969697</v>
+        <v>220.3503313082531</v>
       </c>
       <c r="X42" t="n">
-        <v>421.6969696969697</v>
+        <v>220.3503313082531</v>
       </c>
       <c r="Y42" t="n">
-        <v>213.9366709320158</v>
+        <v>186.0434107622412</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8439,16 +8439,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8521,16 +8521,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>156.2912070328283</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812385</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8670,10 +8670,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>260.7159099194822</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
         <v>230.3462332272727</v>
@@ -8682,10 +8682,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8752,10 +8752,10 @@
         <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>163.5038747293692</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -8764,10 +8764,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>245.0393459944755</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N14" t="n">
-        <v>255.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O14" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P14" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M15" t="n">
-        <v>168.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>167.5457393939394</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>158.5595353283699</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9147,19 +9147,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M17" t="n">
-        <v>230.3462332272727</v>
+        <v>256.8215099922226</v>
       </c>
       <c r="N17" t="n">
-        <v>257.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O17" t="n">
-        <v>258.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
-        <v>258.1016826239564</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>168.6093106869682</v>
       </c>
       <c r="N18" t="n">
-        <v>159.3417120833333</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>166.8504609547084</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,10 +9381,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M20" t="n">
         <v>449.5135334928325</v>
@@ -9466,13 +9466,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>186.8300115967677</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9703,16 +9703,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
-        <v>238.6132356387368</v>
+        <v>238.6269471880057</v>
       </c>
       <c r="Q24" t="n">
         <v>139.9817740860215</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>370.8403453034592</v>
+        <v>369.8307175917693</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10171,19 +10171,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>231.1106999087204</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>360.302996258564</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
@@ -10335,13 +10335,13 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O32" t="n">
-        <v>281.9614083965644</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
         <v>321.7987081714826</v>
@@ -10411,22 +10411,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>353.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>252.3350059713232</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N33" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10648,22 +10648,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>278.351651585322</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>371.3463732493024</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10809,16 +10809,16 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>437.0731727773048</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O38" t="n">
-        <v>380.8001812627454</v>
+        <v>283.1274823473447</v>
       </c>
       <c r="P38" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10885,22 +10885,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>338.0329219811887</v>
       </c>
       <c r="O39" t="n">
-        <v>309.3255008821412</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P39" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11043,10 +11043,10 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
-        <v>417.6612145504504</v>
+        <v>314.1588986527692</v>
       </c>
       <c r="M41" t="n">
-        <v>338.5882684418997</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>343.3554408268194</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>150.2708721503366</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -23038,16 +23038,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>301.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>323.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>343.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>363.3371386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -23075,7 +23075,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>89.33464423649647</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
         <v>89.39663285141508</v>
@@ -23105,7 +23105,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
         <v>171.6831711038378</v>
@@ -23114,13 +23114,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>199.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>225.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
         <v>205.7729852034775</v>
@@ -23181,22 +23181,22 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>63.61835938314394</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
-        <v>201.9455894282815</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V10" t="n">
-        <v>226.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W10" t="n">
         <v>286.522998336591</v>
@@ -23275,16 +23275,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
-        <v>301.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
-        <v>323.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X11" t="n">
-        <v>343.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y11" t="n">
-        <v>363.3371386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="12">
@@ -23309,16 +23309,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>115.1893084894685</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23345,7 +23345,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>145.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
         <v>200.1647286948216</v>
@@ -23388,19 +23388,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.7167873157913</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H13" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23464,16 +23464,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>187.5750895704059</v>
+        <v>187.9095370861751</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23500,13 +23500,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S14" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T14" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U14" t="n">
         <v>251.3456529078365</v>
@@ -23543,7 +23543,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.1684123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
         <v>137.3435171632106</v>
@@ -23591,16 +23591,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
-        <v>206.8005871494253</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W15" t="n">
-        <v>225.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X15" t="n">
-        <v>205.7729852034775</v>
+        <v>180.1526940088467</v>
       </c>
       <c r="Y15" t="n">
-        <v>179.6826957773044</v>
+        <v>183.1163432930735</v>
       </c>
     </row>
     <row r="16">
@@ -23613,7 +23613,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C16" t="n">
-        <v>167.2468210986278</v>
+        <v>166.9499604402799</v>
       </c>
       <c r="D16" t="n">
         <v>148.6154730182124</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.9909793584588</v>
+        <v>142.3706881638279</v>
       </c>
       <c r="H16" t="n">
-        <v>161.9529804647721</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,7 +23655,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
         <v>177.2933913771695</v>
@@ -23689,31 +23689,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>354.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C17" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D17" t="n">
-        <v>326.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E17" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>394.162935096324</v>
+        <v>379.2860204813953</v>
       </c>
       <c r="G17" t="n">
-        <v>387.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>186.1745953211195</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23743,7 +23743,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>195.5058243038152</v>
       </c>
       <c r="U17" t="n">
         <v>251.3456529078365</v>
@@ -23780,16 +23780,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>121.1534037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>109.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>84.23544423649646</v>
+        <v>84.64541897618032</v>
       </c>
       <c r="I18" t="n">
-        <v>61.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23822,13 +23822,13 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>176.610025771793</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>198.3513568206587</v>
       </c>
       <c r="V18" t="n">
-        <v>232.8005871494253</v>
+        <v>205.2105618891091</v>
       </c>
       <c r="W18" t="n">
         <v>251.6949831609196</v>
@@ -23847,7 +23847,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>179.8319801819373</v>
+        <v>152.2419549216212</v>
       </c>
       <c r="C19" t="n">
         <v>167.2468210986278</v>
@@ -23898,19 +23898,19 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>201.5678386764629</v>
       </c>
       <c r="T19" t="n">
-        <v>205.9231218020954</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
-        <v>258.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>224.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>258.522998336591</v>
+        <v>258.9329730762748</v>
       </c>
       <c r="X19" t="n">
         <v>225.7096553890372</v>
@@ -23926,19 +23926,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C20" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
         <v>415.302737515135</v>
@@ -23971,22 +23971,22 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>146.6038018839531</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
-        <v>316.5860768350565</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
         <v>349.240968717413</v>
@@ -23995,7 +23995,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24005,10 +24005,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>40.90767664525444</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
@@ -24029,7 +24029,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24056,22 +24056,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>117.2220797075721</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -24138,7 +24138,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
         <v>286.3190293564909</v>
@@ -24147,7 +24147,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
@@ -24166,22 +24166,22 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
@@ -24211,13 +24211,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>20.80116313523413</v>
       </c>
       <c r="U23" t="n">
         <v>251.3456529078365</v>
@@ -24226,10 +24226,10 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>264.848055459353</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
         <v>386.2379386560536</v>
@@ -24242,7 +24242,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
         <v>172.7084989883157</v>
@@ -24257,10 +24257,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>91.49857956302566</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -24293,25 +24293,25 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>97.91429139426087</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24369,7 +24369,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180149</v>
       </c>
       <c r="S25" t="n">
         <v>224.0165980369723</v>
@@ -24378,7 +24378,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24403,13 +24403,13 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F26" t="n">
         <v>406.8760457417114</v>
@@ -24445,31 +24445,31 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>6.737968800790156</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
-        <v>349.240968717413</v>
+        <v>136.955583073971</v>
       </c>
       <c r="X26" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24488,10 +24488,10 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
-        <v>118.1388564677497</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
         <v>137.3435171632106</v>
@@ -24542,7 +24542,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>67.06409450346541</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -24615,7 +24615,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24627,7 +24627,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y28" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="29">
@@ -24646,7 +24646,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>381.9303700722618</v>
+        <v>291.5414323341854</v>
       </c>
       <c r="F29" t="n">
         <v>406.8760457417114</v>
@@ -24661,7 +24661,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24682,28 +24682,28 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>10.8230495641314</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
         <v>386.2379386560536</v>
@@ -24734,13 +24734,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24764,10 +24764,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>142.6719168639732</v>
+        <v>148.5044553246174</v>
       </c>
       <c r="T30" t="n">
         <v>200.1647286948216</v>
@@ -24779,10 +24779,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
         <v>205.6826957773044</v>
@@ -24837,19 +24837,19 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S31" t="n">
         <v>224.0165980369723</v>
       </c>
       <c r="T31" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
         <v>286.3190293564909</v>
@@ -24880,7 +24880,7 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>165.311041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E32" t="n">
         <v>381.9303700722618</v>
@@ -24889,7 +24889,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24919,19 +24919,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>138.6760617849701</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24940,10 +24940,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>154.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24962,16 +24962,16 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -25010,7 +25010,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>113.9006687582424</v>
+        <v>126.6932313148213</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25022,7 +25022,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25053,10 +25053,10 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I34" t="n">
-        <v>115.622687458563</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
         <v>22.26949182588285</v>
@@ -25080,7 +25080,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S34" t="n">
         <v>224.0165980369723</v>
@@ -25111,7 +25111,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C35" t="n">
         <v>365.2728917710076</v>
@@ -25126,7 +25126,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>415.302737515135</v>
+        <v>203.0173518716929</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
@@ -25168,16 +25168,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>61.97365290783654</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>112.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W35" t="n">
-        <v>134.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>154.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y35" t="n">
         <v>386.2379386560536</v>
@@ -25199,22 +25199,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>10.57773708528137</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>43.99872451040798</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25244,19 +25244,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>10.94138208097482</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25278,7 +25278,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E37" t="n">
-        <v>13.24699506120112</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F37" t="n">
         <v>145.4210480229312</v>
@@ -25311,7 +25311,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>86.16204325169439</v>
@@ -25329,7 +25329,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>252.137643323828</v>
+        <v>121.6721164735665</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
@@ -25354,25 +25354,25 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>354.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E38" t="n">
-        <v>381.9303700722618</v>
+        <v>166.5363723892335</v>
       </c>
       <c r="F38" t="n">
-        <v>406.8760457417114</v>
+        <v>191.4820480586832</v>
       </c>
       <c r="G38" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>210.4758895704059</v>
+        <v>30.74755562573949</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>191.4571760965523</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>8.095849564131356</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>36.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25427,22 +25427,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>89.98082821349723</v>
+        <v>56.4310172934314</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25563,13 +25563,13 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25585,13 +25585,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>169.3095780461377</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>177.288800376852</v>
       </c>
       <c r="D41" t="n">
-        <v>354.683041620683</v>
+        <v>141.25877800334</v>
       </c>
       <c r="E41" t="n">
         <v>381.9303700722618</v>
@@ -25600,16 +25600,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>202.302737515135</v>
+        <v>201.8784738977921</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>180.7039664524135</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25633,10 +25633,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
         <v>223.0958495641314</v>
@@ -25645,7 +25645,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>114.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
         <v>349.240968717413</v>
@@ -25664,7 +25664,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>83.84092366366815</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>172.7084989883157</v>
@@ -25682,13 +25682,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>12.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>171.7188444367526</v>
       </c>
     </row>
     <row r="43">
@@ -25791,7 +25791,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>44.10642379180143</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S43" t="n">
         <v>224.0165980369723</v>
@@ -25800,7 +25800,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350387.4464706169</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350387.4464706169</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350387.4464706169</v>
+        <v>350071.9014065734</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352034.7526374221</v>
+        <v>351708.7869702387</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>507077.4418798315</v>
+        <v>507087.7759459232</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>507077.4418798315</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>507077.4418798315</v>
+        <v>507087.7759459233</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>507077.4418798314</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488273.6054418518</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488273.6054418518</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488273.6054418518</v>
+        <v>488558.5542106443</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486827.1564850841</v>
+        <v>487133.994318434</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75255.18387201249</v>
+        <v>75255.18387201248</v>
       </c>
       <c r="C2" t="n">
         <v>75255.18387201248</v>
       </c>
       <c r="D2" t="n">
-        <v>80408.2149765083</v>
+        <v>75255.18387201248</v>
       </c>
       <c r="E2" t="n">
-        <v>80408.21497650832</v>
+        <v>75255.18387201247</v>
       </c>
       <c r="F2" t="n">
-        <v>80408.21497650829</v>
+        <v>80335.91512409358</v>
       </c>
       <c r="G2" t="n">
-        <v>80785.65708007246</v>
+        <v>80710.96958749177</v>
       </c>
       <c r="H2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="I2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="J2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="K2" t="n">
-        <v>116310.1029597295</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="L2" t="n">
-        <v>112001.6387997295</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="M2" t="n">
-        <v>112001.6387997296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="N2" t="n">
-        <v>112001.6387997296</v>
+        <v>112066.9282188238</v>
       </c>
       <c r="O2" t="n">
-        <v>111670.2184797296</v>
+        <v>111740.5232716417</v>
       </c>
       <c r="P2" t="n">
-        <v>75255.18387201249</v>
+        <v>75255.18387201248</v>
       </c>
     </row>
     <row r="3">
@@ -26319,19 +26319,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>7340.879554832793</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26876.8513828616</v>
+        <v>27440.77263656519</v>
       </c>
       <c r="C4" t="n">
-        <v>26876.8513828616</v>
+        <v>27440.77263656519</v>
       </c>
       <c r="D4" t="n">
-        <v>28777.11938676419</v>
+        <v>27440.77263656519</v>
       </c>
       <c r="E4" t="n">
-        <v>28777.11938676419</v>
+        <v>27440.77263656519</v>
       </c>
       <c r="F4" t="n">
-        <v>28777.11938676419</v>
+        <v>29353.22408421848</v>
       </c>
       <c r="G4" t="n">
-        <v>28916.30759234339</v>
+        <v>29494.39932374348</v>
       </c>
       <c r="H4" t="n">
-        <v>42016.55218480954</v>
+        <v>42895.25425991549</v>
       </c>
       <c r="I4" t="n">
-        <v>42016.55218480954</v>
+        <v>42895.25425991549</v>
       </c>
       <c r="J4" t="n">
-        <v>42016.55218480955</v>
+        <v>42895.2542599155</v>
       </c>
       <c r="K4" t="n">
-        <v>42016.55218480954</v>
+        <v>42895.25425991549</v>
       </c>
       <c r="L4" t="n">
-        <v>40427.73262925399</v>
+        <v>42895.25425991549</v>
       </c>
       <c r="M4" t="n">
-        <v>40427.73262925399</v>
+        <v>42895.2542599155</v>
       </c>
       <c r="N4" t="n">
-        <v>40427.73262925399</v>
+        <v>41297.17839269835</v>
       </c>
       <c r="O4" t="n">
-        <v>40305.5157403651</v>
+        <v>41174.31544585305</v>
       </c>
       <c r="P4" t="n">
-        <v>26876.8513828616</v>
+        <v>27440.77263656519</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.7324891509</v>
+        <v>14186.81123544729</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>14186.81123544729</v>
       </c>
       <c r="D6" t="n">
-        <v>8346.31558974411</v>
+        <v>14186.81123544729</v>
       </c>
       <c r="E6" t="n">
-        <v>50050.29558974413</v>
+        <v>47814.41123544727</v>
       </c>
       <c r="F6" t="n">
-        <v>50050.2955897441</v>
+        <v>42084.09778040875</v>
       </c>
       <c r="G6" t="n">
-        <v>49618.77948772907</v>
+        <v>48999.22216652771</v>
       </c>
       <c r="H6" t="n">
-        <v>2171.433774920024</v>
+        <v>1179.760605923824</v>
       </c>
       <c r="I6" t="n">
-        <v>59640.75077492003</v>
+        <v>58763.54774825554</v>
       </c>
       <c r="J6" t="n">
-        <v>59640.75077492003</v>
+        <v>58763.54774825549</v>
       </c>
       <c r="K6" t="n">
-        <v>59640.75077492</v>
+        <v>58763.54774825557</v>
       </c>
       <c r="L6" t="n">
-        <v>58501.90617047556</v>
+        <v>58763.54774825551</v>
       </c>
       <c r="M6" t="n">
-        <v>58501.90617047562</v>
+        <v>58763.54774825551</v>
       </c>
       <c r="N6" t="n">
-        <v>58501.90617047559</v>
+        <v>57673.79476699735</v>
       </c>
       <c r="O6" t="n">
-        <v>58414.30273936447</v>
+        <v>57590.01259785415</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.3324891509</v>
+        <v>47814.41123544729</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26904,37 +26904,37 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,19 +27191,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35094,16 +35094,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35176,16 +35176,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26.00000000000018</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,10 +35325,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -35337,10 +35337,10 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35407,10 +35407,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -35419,10 +35419,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35802,19 +35802,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
-        <v>26.86868686868686</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,25 +35878,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>26.86868686868686</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,13 +36121,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>55.48829951343436</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36358,16 +36358,16 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
-        <v>104.6388282244066</v>
+        <v>104.6525397736754</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>232.285965523585</v>
+        <v>231.276337811895</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36826,19 +36826,19 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>99.76898782538704</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
@@ -36990,13 +36990,13 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O32" t="n">
-        <v>51.86319697487763</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
         <v>90.5657124162131</v>
@@ -37066,22 +37066,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>215</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>110.2009720493049</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>136.2176176633037</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37464,16 +37464,16 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>206.726939550032</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O38" t="n">
-        <v>150.7019698410586</v>
+        <v>53.02927092565796</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37540,22 +37540,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>206.6912098978553</v>
       </c>
       <c r="O39" t="n">
-        <v>166.7292564376967</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P39" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37698,10 +37698,10 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
-        <v>181.8947995804632</v>
+        <v>78.39248368278189</v>
       </c>
       <c r="M41" t="n">
-        <v>108.242035214627</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>204.8010610469452</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>7.674627705892183</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
